--- a/cypress/fixtures/File/generated/Software Purchase _ Service Agreement.xlsx
+++ b/cypress/fixtures/File/generated/Software Purchase _ Service Agreement.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="83">
   <si>
     <t>name</t>
   </si>
@@ -64,6 +64,12 @@
     <t>Factory GSTIN No.</t>
   </si>
   <si>
+    <t>Registered Office Address</t>
+  </si>
+  <si>
+    <t>Corporate Office Address</t>
+  </si>
+  <si>
     <t>Function</t>
   </si>
   <si>
@@ -160,9 +166,6 @@
     <t>Fixed Term</t>
   </si>
   <si>
-    <t>Initial Renewal Date</t>
-  </si>
-  <si>
     <t>Contract Expiration Date</t>
   </si>
   <si>
@@ -188,6 +191,12 @@
   </si>
   <si>
     <t>Registered Office</t>
+  </si>
+  <si>
+    <t>Counterparty Registered Office Address</t>
+  </si>
+  <si>
+    <t>if Registered office option is selected in above field</t>
   </si>
   <si>
     <t>Counterparty GSTIN No.</t>
@@ -631,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -720,29 +729,29 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -750,10 +759,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
@@ -761,10 +770,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
@@ -772,10 +781,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
@@ -783,10 +792,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
@@ -794,10 +803,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
@@ -805,21 +814,21 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
@@ -827,90 +836,90 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
         <v>39</v>
       </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
         <v>42</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
         <v>50</v>
       </c>
-      <c r="B25" t="s">
-        <v>45</v>
-      </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +927,10 @@
         <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,21 +949,21 @@
         <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
         <v>55</v>
       </c>
-      <c r="B29" t="s">
-        <v>14</v>
-      </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,21 +982,21 @@
         <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s">
         <v>59</v>
       </c>
-      <c r="B32" t="s">
-        <v>14</v>
-      </c>
       <c r="C32" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,7 +1004,7 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
@@ -1003,13 +1012,13 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,7 +1037,7 @@
         <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
@@ -1036,7 +1045,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -1047,10 +1056,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C38" t="s">
         <v>8</v>
@@ -1072,15 +1081,15 @@
         <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -1091,7 +1100,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -1102,7 +1111,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -1113,24 +1122,24 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1138,32 +1147,54 @@
         <v>76</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
         <v>77</v>
       </c>
-      <c r="B47" t="s">
-        <v>74</v>
-      </c>
       <c r="C47" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" t="s">
         <v>78</v>
       </c>
-      <c r="B48" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" t="s">
-        <v>79</v>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
